--- a/financials/2025/Balance Sheet.xlsx
+++ b/financials/2025/Balance Sheet.xlsx
@@ -164,11 +164,6 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
       <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -178,6 +173,11 @@
       <sz val="19"/>
       <color indexed="9"/>
       <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="19"/>
+      <color indexed="9"/>
+      <name val="Montserrat-Regular"/>
     </font>
     <font>
       <sz val="19"/>
@@ -255,12 +255,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="12"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
@@ -271,8 +265,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="15"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -302,45 +302,44 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="11"/>
+      <right>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="11"/>
       </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
       </left>
-      <right style="thin">
-        <color indexed="11"/>
+      <right/>
+      <top>
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top>
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right>
+        <color indexed="8"/>
       </right>
-      <top style="thin">
-        <color indexed="9"/>
+      <top>
+        <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -361,45 +360,84 @@
     </border>
     <border>
       <left/>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </right>
-      <top style="thin">
-        <color indexed="11"/>
+      <top>
+        <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
+      <right/>
+      <top>
+        <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -407,172 +445,45 @@
       <right style="thin">
         <color indexed="11"/>
       </right>
-      <top style="thin">
-        <color indexed="11"/>
+      <top>
+        <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="11"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="15"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="15"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="15"/>
+        <color indexed="16"/>
       </right>
       <top/>
       <bottom/>
@@ -580,7 +491,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="16"/>
       </left>
       <right style="thin">
         <color indexed="11"/>
@@ -591,19 +502,17 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="16"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="9"/>
       </right>
@@ -615,34 +524,26 @@
       <left style="thin">
         <color indexed="9"/>
       </left>
+      <right/>
+      <top/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -652,20 +553,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
       </left>
       <right style="thin">
         <color indexed="9"/>
@@ -680,14 +568,78 @@
       <left style="thin">
         <color indexed="9"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="9"/>
       </right>
+      <top/>
+      <bottom>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top>
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right/>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="9"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left>
+        <color indexed="8"/>
+      </left>
+      <right>
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -697,27 +649,27 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
@@ -725,11 +677,20 @@
     <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
@@ -737,13 +698,13 @@
     <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -755,16 +716,16 @@
     <xf numFmtId="0" fontId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="59" fontId="8" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="8" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="59" fontId="8" fillId="3" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -773,247 +734,226 @@
     <xf numFmtId="0" fontId="0" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="7" fillId="3" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="10" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="7" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="60" fontId="10" fillId="3" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="60" fontId="10" fillId="6" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="60" fontId="10" fillId="6" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="12" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="60" fontId="9" fillId="4" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="10" fillId="5" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="10" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="12" fillId="6" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="34" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="35" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="60" fontId="10" fillId="3" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="12" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="60" fontId="9" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" fillId="5" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="6" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="60" fontId="12" fillId="6" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="60" fontId="10" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="60" fontId="7" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1035,7 +975,8 @@
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ff95b3d7"/>
-      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffe9e9e9"/>
+      <rgbColor rgb="ffbfbfbf"/>
       <rgbColor rgb="ff4f81bd"/>
       <rgbColor rgb="ffdce6f1"/>
       <rgbColor rgb="ffb8cce4"/>
@@ -2083,14 +2024,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L96"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="11.6016" style="1" customWidth="1"/>
     <col min="2" max="4" width="14.8125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.4219" style="1" customWidth="1"/>
-    <col min="6" max="12" width="14.8125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="6" max="11" width="14.8125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="73" customHeight="1">
@@ -2102,73 +2046,69 @@
         <v>1</v>
       </c>
       <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="8"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="9"/>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="13"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="18"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" t="s" s="19">
+      <c r="A4" t="s" s="22">
         <v>2</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21">
-        <v>45292</v>
-      </c>
-      <c r="D4" t="s" s="22">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24">
+        <v>45658</v>
+      </c>
+      <c r="D4" t="s" s="25">
         <v>3</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="26">
         <v>46022</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="G4" t="s" s="25">
+      <c r="F4" s="27"/>
+      <c r="G4" t="s" s="28">
         <v>4</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="30"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="s" s="28">
+      <c r="A5" t="s" s="22">
         <v>5</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" t="s" s="30">
+      <c r="B5" s="23"/>
+      <c r="C5" t="s" s="25">
         <v>6</v>
       </c>
       <c r="D5" s="31"/>
@@ -2181,1408 +2121,380 @@
       <c r="I5" s="35"/>
       <c r="J5" s="35"/>
       <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="38"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="38"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41"/>
-      <c r="H6" t="s" s="42">
+      <c r="F6" s="33"/>
+      <c r="G6" s="40"/>
+      <c r="H6" t="s" s="41">
         <v>8</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44">
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="43">
         <v>0</v>
       </c>
-      <c r="L6" s="13"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" t="s" s="45">
+      <c r="A7" t="s" s="44">
         <v>9</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="46"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="40"/>
       <c r="H7" t="s" s="47">
         <v>10</v>
       </c>
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
-      <c r="K7" s="49">
+      <c r="K7" s="43">
         <v>0</v>
       </c>
-      <c r="L7" s="13"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" t="s" s="50">
+      <c r="A8" t="s" s="49">
         <v>11</v>
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="48"/>
-      <c r="H8" t="s" s="51">
+      <c r="E8" s="50"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="51"/>
+      <c r="H8" t="s" s="47">
         <v>12</v>
       </c>
       <c r="I8" s="48"/>
       <c r="J8" s="48"/>
-      <c r="K8" s="52">
+      <c r="K8" s="43">
         <v>0</v>
       </c>
-      <c r="L8" s="13"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="41"/>
-      <c r="B9" t="s" s="42">
+      <c r="A9" s="52"/>
+      <c r="B9" t="s" s="41">
         <v>13</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="53">
         <v>8.710000000000001</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="54"/>
-      <c r="H9" t="s" s="55">
+      <c r="F9" s="33"/>
+      <c r="G9" s="51"/>
+      <c r="H9" t="s" s="54">
         <v>14</v>
       </c>
-      <c r="I9" s="56"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="58">
+      <c r="I9" s="55"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="57">
         <f>SUM(K6:K8)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="37"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="46"/>
-      <c r="B10" t="s" s="59">
+      <c r="A10" s="52"/>
+      <c r="B10" t="s" s="41">
         <v>15</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="61">
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="53">
         <v>0</v>
       </c>
       <c r="F10" s="33"/>
-      <c r="G10" t="s" s="62">
+      <c r="G10" t="s" s="58">
         <v>16</v>
       </c>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="37"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="60"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="46"/>
-      <c r="B11" t="s" s="59">
+      <c r="A11" s="52"/>
+      <c r="B11" t="s" s="41">
         <v>17</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="61">
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="53">
         <v>0</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="64"/>
-      <c r="H11" t="s" s="65">
+      <c r="F11" s="33"/>
+      <c r="G11" s="51"/>
+      <c r="H11" t="s" s="47">
         <v>18</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="44">
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="43">
         <v>0</v>
       </c>
-      <c r="L11" s="13"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="46"/>
-      <c r="B12" t="s" s="66">
+      <c r="A12" s="52"/>
+      <c r="B12" t="s" s="41">
         <v>19</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="68">
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="53">
         <v>1000.02</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="48"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="51"/>
       <c r="H12" t="s" s="47">
         <v>20</v>
       </c>
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
-      <c r="K12" s="49">
+      <c r="K12" s="43">
         <v>0</v>
       </c>
-      <c r="L12" s="13"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="69"/>
-      <c r="B13" t="s" s="55">
+      <c r="A13" s="52"/>
+      <c r="B13" t="s" s="54">
         <v>21</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="58">
+      <c r="C13" s="62"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="64">
         <f>SUM(E9:E12)</f>
         <v>1008.73</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="48"/>
-      <c r="H13" t="s" s="51">
+      <c r="F13" s="33"/>
+      <c r="G13" s="51"/>
+      <c r="H13" t="s" s="47">
         <v>22</v>
       </c>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="52">
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="43">
         <v>0</v>
       </c>
-      <c r="L13" s="13"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="s" s="73">
+      <c r="A14" t="s" s="65">
         <v>23</v>
       </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="54"/>
-      <c r="H14" t="s" s="55">
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="51"/>
+      <c r="H14" t="s" s="54">
         <v>24</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="58">
+      <c r="I14" s="62"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="57">
         <f>SUM(K11:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="37"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="41"/>
-      <c r="B15" t="s" s="65">
+      <c r="A15" s="52"/>
+      <c r="B15" t="s" s="47">
         <v>25</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="53">
         <v>0</v>
       </c>
       <c r="F15" s="33"/>
-      <c r="G15" t="s" s="74">
+      <c r="G15" t="s" s="67">
         <v>26</v>
       </c>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="77">
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="70">
         <f>K9+K14</f>
         <v>0</v>
       </c>
-      <c r="L15" s="37"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="46"/>
+      <c r="A16" s="52"/>
       <c r="B16" t="s" s="47">
         <v>27</v>
       </c>
       <c r="C16" s="48"/>
       <c r="D16" s="48"/>
-      <c r="E16" s="61">
+      <c r="E16" s="53">
         <f>(70325.28+238.7539254+153.0086232+178.4131997)*0.200721</f>
         <v>14230.2067732545</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="81"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="46"/>
+      <c r="A17" s="52"/>
       <c r="B17" t="s" s="47">
         <v>28</v>
       </c>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
-      <c r="E17" s="61">
+      <c r="E17" s="53">
         <v>2250</v>
       </c>
       <c r="F17" s="33"/>
-      <c r="G17" t="s" s="25">
+      <c r="G17" t="s" s="74">
         <v>29</v>
       </c>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="37"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="75"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="46"/>
-      <c r="B18" t="s" s="51">
+      <c r="A18" s="52"/>
+      <c r="B18" t="s" s="47">
         <v>30</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="68">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="53">
         <v>0</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" t="s" s="65">
+      <c r="F18" s="33"/>
+      <c r="G18" t="s" s="76">
         <v>31</v>
       </c>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="44">
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="43">
         <v>0</v>
       </c>
-      <c r="L18" s="13"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="54"/>
-      <c r="B19" t="s" s="55">
+      <c r="A19" s="77"/>
+      <c r="B19" t="s" s="54">
         <v>32</v>
       </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="58">
+      <c r="C19" s="62"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="64">
         <f>SUM(E15:E18)</f>
         <v>16480.2067732545</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" t="s" s="47">
+      <c r="F19" s="33"/>
+      <c r="G19" t="s" s="76">
         <v>33</v>
       </c>
       <c r="H19" s="48"/>
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
-      <c r="K19" s="49">
+      <c r="K19" s="43">
         <f>9900+520.69</f>
         <v>10420.69</v>
       </c>
-      <c r="L19" s="13"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="s" s="73">
+      <c r="A20" t="s" s="65">
         <v>34</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="84">
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="79">
         <f>0.0006*27129.5734563</f>
         <v>16.277744073780</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" t="s" s="51">
+      <c r="F20" s="33"/>
+      <c r="G20" t="s" s="76">
         <v>35</v>
       </c>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="85">
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="80">
         <v>-5895.31</v>
       </c>
-      <c r="L20" s="13"/>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="A21" t="s" s="86">
+      <c r="A21" t="s" s="81">
         <v>36</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="89">
+      <c r="B21" s="82"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="84">
         <f>E13+E19+E20</f>
         <v>17505.2145173283</v>
       </c>
-      <c r="F21" s="90"/>
-      <c r="G21" t="s" s="74">
+      <c r="F21" s="33"/>
+      <c r="G21" t="s" s="67">
         <v>37</v>
       </c>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="77">
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="70">
         <f>SUM(K18:K20)</f>
         <v>4525.38</v>
       </c>
-      <c r="L21" s="37"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="94"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="91"/>
     </row>
     <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="98"/>
-      <c r="B23" t="s" s="99">
+      <c r="A23" s="92"/>
+      <c r="B23" t="s" s="93">
         <v>38</v>
       </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="92"/>
     </row>
     <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="46"/>
-      <c r="B24" t="s" s="101">
+      <c r="A24" s="97"/>
+      <c r="B24" t="s" s="98">
         <v>39</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-    </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-    </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="102"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-    </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="46"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="46"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-    </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-    </row>
-    <row r="32" ht="14" customHeight="1">
-      <c r="A32" s="46"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="46"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46"/>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="46"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-    </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="46"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="102"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="46"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="102"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
-    </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="46"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
-    </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="46"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-    </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="46"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="102"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="46"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="102"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="48"/>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="48"/>
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="48"/>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="48"/>
-      <c r="B44" s="48"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="48"/>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="48"/>
-      <c r="B46" s="48"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46"/>
-    </row>
-    <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="48"/>
-      <c r="B47" s="48"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="103"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="48"/>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="103"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="48"/>
-      <c r="B49" s="48"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="48"/>
-      <c r="B50" s="48"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="48"/>
-      <c r="B51" s="48"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="48"/>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="48"/>
-      <c r="B53" s="48"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="103"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-    </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="48"/>
-      <c r="B54" s="48"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="103"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="48"/>
-      <c r="B55" s="48"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="103"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="48"/>
-      <c r="B56" s="48"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="103"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="48"/>
-      <c r="B57" s="48"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="103"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="48"/>
-      <c r="B58" s="48"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="103"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="48"/>
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="103"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="48"/>
-      <c r="B60" s="48"/>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="48"/>
-      <c r="B61" s="48"/>
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="103"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="48"/>
-      <c r="B62" s="48"/>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="46"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-      <c r="L62" s="46"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="48"/>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="103"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="46"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="48"/>
-      <c r="B64" s="48"/>
-      <c r="C64" s="48"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="103"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="48"/>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="103"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
-      <c r="L65" s="46"/>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="48"/>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="103"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="48"/>
-      <c r="B67" s="48"/>
-      <c r="C67" s="48"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="103"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="48"/>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="103"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
-      <c r="L68" s="46"/>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="48"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="103"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46"/>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
-      <c r="L69" s="46"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="103"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="46"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="103"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46"/>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="48"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="103"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="46"/>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="48"/>
-      <c r="B73" s="48"/>
-      <c r="C73" s="48"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="103"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="46"/>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
-      <c r="L73" s="46"/>
-    </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="104"/>
-      <c r="B74" s="104"/>
-      <c r="C74" s="104"/>
-      <c r="D74" s="104"/>
-      <c r="E74" s="105"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46"/>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
-      <c r="L74" s="46"/>
-    </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="104"/>
-      <c r="B75" s="104"/>
-      <c r="C75" s="104"/>
-      <c r="D75" s="104"/>
-      <c r="E75" s="105"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="104"/>
-      <c r="B76" s="104"/>
-      <c r="C76" s="104"/>
-      <c r="D76" s="104"/>
-      <c r="E76" s="105"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="46"/>
-    </row>
-    <row r="77" ht="14" customHeight="1">
-      <c r="A77" s="104"/>
-      <c r="B77" s="104"/>
-      <c r="C77" s="104"/>
-      <c r="D77" s="104"/>
-      <c r="E77" s="105"/>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="46"/>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
-      <c r="L77" s="46"/>
-    </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="104"/>
-      <c r="B78" s="104"/>
-      <c r="C78" s="104"/>
-      <c r="D78" s="104"/>
-      <c r="E78" s="105"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46"/>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="104"/>
-      <c r="B79" s="104"/>
-      <c r="C79" s="104"/>
-      <c r="D79" s="104"/>
-      <c r="E79" s="105"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
-    </row>
-    <row r="80" ht="14" customHeight="1">
-      <c r="A80" s="104"/>
-      <c r="B80" s="104"/>
-      <c r="C80" s="104"/>
-      <c r="D80" s="104"/>
-      <c r="E80" s="105"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="46"/>
-    </row>
-    <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="104"/>
-      <c r="B81" s="104"/>
-      <c r="C81" s="104"/>
-      <c r="D81" s="104"/>
-      <c r="E81" s="105"/>
-      <c r="F81" s="46"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="46"/>
-      <c r="I81" s="46"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
-      <c r="L81" s="46"/>
-    </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="104"/>
-      <c r="B82" s="104"/>
-      <c r="C82" s="104"/>
-      <c r="D82" s="104"/>
-      <c r="E82" s="105"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="46"/>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="104"/>
-      <c r="B83" s="104"/>
-      <c r="C83" s="104"/>
-      <c r="D83" s="104"/>
-      <c r="E83" s="105"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-    </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="104"/>
-      <c r="B84" s="104"/>
-      <c r="C84" s="104"/>
-      <c r="D84" s="104"/>
-      <c r="E84" s="105"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="46"/>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
-      <c r="L84" s="46"/>
-    </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="104"/>
-      <c r="B85" s="104"/>
-      <c r="C85" s="104"/>
-      <c r="D85" s="104"/>
-      <c r="E85" s="105"/>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46"/>
-      <c r="I85" s="46"/>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
-      <c r="L85" s="46"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="104"/>
-      <c r="B86" s="104"/>
-      <c r="C86" s="104"/>
-      <c r="D86" s="104"/>
-      <c r="E86" s="105"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="46"/>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-      <c r="L86" s="46"/>
-    </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="104"/>
-      <c r="B87" s="104"/>
-      <c r="C87" s="104"/>
-      <c r="D87" s="104"/>
-      <c r="E87" s="105"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="104"/>
-      <c r="B88" s="104"/>
-      <c r="C88" s="104"/>
-      <c r="D88" s="104"/>
-      <c r="E88" s="105"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
-      <c r="L88" s="46"/>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="104"/>
-      <c r="B89" s="104"/>
-      <c r="C89" s="104"/>
-      <c r="D89" s="104"/>
-      <c r="E89" s="105"/>
-      <c r="F89" s="46"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="46"/>
-      <c r="I89" s="46"/>
-      <c r="J89" s="46"/>
-      <c r="K89" s="46"/>
-      <c r="L89" s="46"/>
-    </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="104"/>
-      <c r="B90" s="104"/>
-      <c r="C90" s="104"/>
-      <c r="D90" s="104"/>
-      <c r="E90" s="105"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="46"/>
-    </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="104"/>
-      <c r="B91" s="104"/>
-      <c r="C91" s="104"/>
-      <c r="D91" s="104"/>
-      <c r="E91" s="105"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
-      <c r="L91" s="46"/>
-    </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="104"/>
-      <c r="B92" s="104"/>
-      <c r="C92" s="104"/>
-      <c r="D92" s="104"/>
-      <c r="E92" s="105"/>
-      <c r="F92" s="46"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="46"/>
-      <c r="J92" s="46"/>
-      <c r="K92" s="46"/>
-      <c r="L92" s="46"/>
-    </row>
-    <row r="93" ht="14" customHeight="1">
-      <c r="A93" s="104"/>
-      <c r="B93" s="104"/>
-      <c r="C93" s="104"/>
-      <c r="D93" s="104"/>
-      <c r="E93" s="105"/>
-      <c r="F93" s="46"/>
-      <c r="G93" s="46"/>
-      <c r="H93" s="46"/>
-      <c r="I93" s="46"/>
-      <c r="J93" s="46"/>
-      <c r="K93" s="46"/>
-      <c r="L93" s="46"/>
-    </row>
-    <row r="94" ht="14" customHeight="1">
-      <c r="A94" s="104"/>
-      <c r="B94" s="104"/>
-      <c r="C94" s="104"/>
-      <c r="D94" s="104"/>
-      <c r="E94" s="105"/>
-      <c r="F94" s="46"/>
-      <c r="G94" s="46"/>
-      <c r="H94" s="46"/>
-      <c r="I94" s="46"/>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-      <c r="L94" s="46"/>
-    </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="104"/>
-      <c r="B95" s="104"/>
-      <c r="C95" s="104"/>
-      <c r="D95" s="104"/>
-      <c r="E95" s="105"/>
-      <c r="F95" s="46"/>
-      <c r="G95" s="46"/>
-      <c r="H95" s="46"/>
-      <c r="I95" s="46"/>
-      <c r="J95" s="46"/>
-      <c r="K95" s="46"/>
-      <c r="L95" s="46"/>
-    </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="104"/>
-      <c r="B96" s="104"/>
-      <c r="C96" s="104"/>
-      <c r="D96" s="104"/>
-      <c r="E96" s="105"/>
-      <c r="F96" s="46"/>
-      <c r="G96" s="46"/>
-      <c r="H96" s="46"/>
-      <c r="I96" s="46"/>
-      <c r="J96" s="46"/>
-      <c r="K96" s="46"/>
-      <c r="L96" s="46"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="97"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="45">
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A20:D20"/>
@@ -3607,8 +2519,7 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F4:F22"/>
-    <mergeCell ref="F1:L3"/>
+    <mergeCell ref="F1:K3"/>
     <mergeCell ref="G16:K16"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="G19:J19"/>
@@ -3628,12 +2539,9 @@
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="H11:J11"/>
-    <mergeCell ref="L4:L22"/>
+    <mergeCell ref="F4:F21"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="80" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
 </worksheet>
 </file>